--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Pnl A/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Pnl A/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.53772</v>
+        <v>16.74255</v>
       </c>
       <c r="D2" t="n">
-        <v>16.55009</v>
+        <v>16.43018</v>
       </c>
       <c r="E2" t="n">
-        <v>16.40636</v>
+        <v>16.52191</v>
       </c>
       <c r="F2" t="n">
-        <v>42.19244</v>
+        <v>43.11902</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05016</v>
+        <v>0.04972</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78117</v>
+        <v>1.81299</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.33372</v>
+        <v>16.56585</v>
       </c>
       <c r="D3" t="n">
-        <v>16.1006</v>
+        <v>16.21058</v>
       </c>
       <c r="E3" t="n">
-        <v>16.67943</v>
+        <v>16.36994</v>
       </c>
       <c r="F3" t="n">
-        <v>42.48399</v>
+        <v>42.02522</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04914</v>
+        <v>0.04979</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80051</v>
+        <v>1.76336</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.2888</v>
+        <v>16.69515</v>
       </c>
       <c r="D4" t="n">
-        <v>16.61241</v>
+        <v>16.36372</v>
       </c>
       <c r="E4" t="n">
-        <v>16.90067</v>
+        <v>16.41429</v>
       </c>
       <c r="F4" t="n">
-        <v>41.89391</v>
+        <v>41.36734</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05007</v>
+        <v>0.04952</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83594</v>
+        <v>1.81078</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.54043</v>
+        <v>16.77125</v>
       </c>
       <c r="D5" t="n">
-        <v>16.80741</v>
+        <v>16.17532</v>
       </c>
       <c r="E5" t="n">
-        <v>16.18186</v>
+        <v>16.71727</v>
       </c>
       <c r="F5" t="n">
-        <v>41.56403</v>
+        <v>41.82057</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04914</v>
+        <v>0.04986</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79409</v>
+        <v>1.79351</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.2914</v>
+        <v>16.72592</v>
       </c>
       <c r="D6" t="n">
-        <v>16.52769</v>
+        <v>16.44041</v>
       </c>
       <c r="E6" t="n">
-        <v>16.5214</v>
+        <v>16.47001</v>
       </c>
       <c r="F6" t="n">
-        <v>42.29179</v>
+        <v>41.11673</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05021</v>
+        <v>0.0508</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81582</v>
+        <v>1.79414</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.62886</v>
+        <v>16.74413</v>
       </c>
       <c r="D7" t="n">
-        <v>16.2566</v>
+        <v>16.1706</v>
       </c>
       <c r="E7" t="n">
-        <v>16.39646</v>
+        <v>16.6455</v>
       </c>
       <c r="F7" t="n">
-        <v>42.13846</v>
+        <v>41.49554</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04991</v>
+        <v>0.04873</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8047</v>
+        <v>1.80371</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.49219</v>
+        <v>16.79821</v>
       </c>
       <c r="D8" t="n">
-        <v>16.26815</v>
+        <v>16.42787</v>
       </c>
       <c r="E8" t="n">
-        <v>16.52003</v>
+        <v>16.43326</v>
       </c>
       <c r="F8" t="n">
-        <v>41.30839</v>
+        <v>42.57599</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0491</v>
+        <v>0.05003</v>
       </c>
       <c r="H8" t="n">
-        <v>1.76853</v>
+        <v>1.7826</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.65613</v>
+        <v>16.6662</v>
       </c>
       <c r="D9" t="n">
-        <v>15.79786</v>
+        <v>16.35559</v>
       </c>
       <c r="E9" t="n">
-        <v>16.35922</v>
+        <v>16.48316</v>
       </c>
       <c r="F9" t="n">
-        <v>41.26147</v>
+        <v>41.92613</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04984</v>
+        <v>0.04936</v>
       </c>
       <c r="H9" t="n">
-        <v>1.76906</v>
+        <v>1.80908</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.61348</v>
+        <v>16.66532</v>
       </c>
       <c r="D10" t="n">
-        <v>16.40312</v>
+        <v>16.43214</v>
       </c>
       <c r="E10" t="n">
-        <v>16.50451</v>
+        <v>16.63535</v>
       </c>
       <c r="F10" t="n">
-        <v>42.28218</v>
+        <v>41.90662</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05008</v>
+        <v>0.04977</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83291</v>
+        <v>1.82675</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6046899999999999</v>
+        <v>0.6126200000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.08614</v>
+        <v>1.1111</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.58792</v>
+        <v>0.59935</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0863</v>
+        <v>1.105</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6009</v>
+        <v>0.58966</v>
       </c>
       <c r="D14" t="n">
-        <v>1.08874</v>
+        <v>1.08386</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.59817</v>
+        <v>0.59434</v>
       </c>
       <c r="D15" t="n">
-        <v>1.08339</v>
+        <v>1.09727</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60003</v>
+        <v>0.60454</v>
       </c>
       <c r="D16" t="n">
-        <v>1.09707</v>
+        <v>1.09038</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5991300000000001</v>
+        <v>0.58901</v>
       </c>
       <c r="D17" t="n">
-        <v>1.09823</v>
+        <v>1.09448</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.5984699999999999</v>
+        <v>0.6071</v>
       </c>
       <c r="D18" t="n">
-        <v>1.10178</v>
+        <v>1.08904</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60608</v>
+        <v>0.60419</v>
       </c>
       <c r="D19" t="n">
-        <v>1.08582</v>
+        <v>1.09092</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.59893</v>
+        <v>0.60183</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1217</v>
+        <v>1.11087</v>
       </c>
     </row>
   </sheetData>
